--- a/public/modelos/modelo-comercial.xlsx
+++ b/public/modelos/modelo-comercial.xlsx
@@ -6,10 +6,15 @@
     <sheet name="Instruções" sheetId="1" r:id="rId1"/>
     <sheet name="Funil" sheetId="2" r:id="rId2"/>
     <sheet name="Financeiro" sheetId="3" r:id="rId3"/>
-    <sheet name="Canais" sheetId="4" r:id="rId4"/>
-    <sheet name="Serviços" sheetId="5" r:id="rId5"/>
-    <sheet name="Indicadores" sheetId="6" r:id="rId6"/>
-    <sheet name="Insights" sheetId="7" r:id="rId7"/>
+    <sheet name="Clientes" sheetId="4" r:id="rId4"/>
+    <sheet name="Canais" sheetId="5" r:id="rId5"/>
+    <sheet name="Serviços" sheetId="6" r:id="rId6"/>
+    <sheet name="Profissionais" sheetId="7" r:id="rId7"/>
+    <sheet name="Oportunidades" sheetId="8" r:id="rId8"/>
+    <sheet name="Plano de ação" sheetId="9" r:id="rId9"/>
+    <sheet name="Indicadores" sheetId="10" r:id="rId10"/>
+    <sheet name="Insights" sheetId="11" r:id="rId11"/>
+    <sheet name="Contexto" sheetId="12" r:id="rId12"/>
   </sheets>
 </workbook>
 </file>
@@ -403,49 +408,213 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A10"/>
   <cols>
-    <col min="1" max="1" width="110.83203125" customWidth="1"/>
+    <col min="1" max="1" width="130.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Modelo Portal Look — Relatório Comercial</v>
+        <v>Modelo Portal Look — Relatório Comercial (modelo único)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Cada aba é opcional, exceto Funil. Use uma linha por período (mês) e item.</v>
+        <v>Cada aba é opcional, exceto Funil. Apague (ou deixe vazia) a aba que o cliente não usa: a seção some do portal. Use uma linha por mês e item.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Funil: as colunas depois de Período são as etapas, na ordem (Leads, Agendamentos, Comparecimentos… — use os nomes do cliente).</v>
+        <v>Funil: as colunas depois de Período são as etapas, na ordem (Leads, Agendamentos, Comparecimentos… — use os nomes do cliente). Vazio = não registrado (diferente de zero).</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Deixe a célula vazia quando a etapa não foi registrada (diferente de zero).</v>
+        <v>Financeiro: Receita, Investimento em mídia, Receita atribuída (só a receita dos canais pagos, quando o retorno deve considerar só a mídia) e Vendas.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Canais — Tipo: Mídia paga, Orgânico, Indicação, Recorrente, Plataforma, Offline, Parceria ou Outro.</v>
+        <v>Clientes: Novos clientes e Clientes recorrentes de cada mês.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Abas extras (Serviços, Profissionais, Unidades, Produtos…) viram detalhamentos automaticamente.</v>
+        <v>Canais — uma linha por canal e mês: Leads, Comparecimentos, Receita e Investimento. Tipo: Mídia paga, Orgânico, Indicação, Recorrente, Plataforma, Offline, Parceria ou Outro. O ROI e a participação de cada canal são calculados pelo portal.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Insights — Tipo: Positivo, Atenção, Recomendação ou Neutro.</v>
+        <v>Detalhamentos: qualquer aba com números vira um ranking com o nome dela — Serviços, Profissionais, Terapeutas, Massagens, Procedimentos, Unidades… Colunas: o nome do item, Atendimentos (ou Quantidade), Receita e, se quiser, Status (Ativa, Inativa, Destaque).</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Tabelas livres: Oportunidades, Plano de ação, Próximos passos, Motivos de perda (ou qualquer aba sem números) aparecem como vieram, no mês.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Indicadores: só o que o portal não calcula (ex.: Marcações para o mês seguinte). Acumulados, conversões, ticket médio, ROI e participação dos canais já são calculados — não precisam ser digitados.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Insights — Tipo: Positivo, Atenção, Recomendação ou Neutro. Contexto: um aviso no topo do mês (ex.: mês parcial).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A10"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Período</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Indicador</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Valor</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Formato</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Direção</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>09/2026</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Marcações para o mês seguinte</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Número</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Maior é melhor</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Período</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Título</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Descrição</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>09/2026</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Positivo</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Mais comparecimentos</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Os comparecimentos subiram em relação a agosto.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>09/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Recomendação</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Reforçar indicação</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Indicação segue como o canal de maior conversão.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Período</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Título</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Descrição</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>08/2026</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Agenda reduzida</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Atendimentos suspensos de 18 a 22/08.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -567,6 +736,55 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Período</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Novos clientes</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Clientes recorrentes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>08/2026</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>09/2026</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G6"/>
   <cols>
@@ -715,7 +933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <cols>
@@ -774,15 +992,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,16 +1008,16 @@
         <v>Período</v>
       </c>
       <c r="B1" t="str">
-        <v>Indicador</v>
+        <v>Profissional</v>
       </c>
       <c r="C1" t="str">
-        <v>Valor</v>
+        <v>Atendimentos</v>
       </c>
       <c r="D1" t="str">
-        <v>Formato</v>
+        <v>Receita</v>
       </c>
       <c r="E1" t="str">
-        <v>Direção</v>
+        <v>Status</v>
       </c>
     </row>
     <row r="2">
@@ -807,33 +1025,50 @@
         <v>09/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>Marcações para o mês seguinte</v>
+        <v>Dra. Ana</v>
       </c>
       <c r="C2">
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>2975</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Destaque</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>09/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Dr. Bruno</v>
+      </c>
+      <c r="C3">
         <v>4</v>
       </c>
-      <c r="D2" t="str">
-        <v>Número</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Maior é melhor</v>
+      <c r="D3">
+        <v>1700</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Ativo</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -841,13 +1076,13 @@
         <v>Período</v>
       </c>
       <c r="B1" t="str">
-        <v>Tipo</v>
+        <v>Origem</v>
       </c>
       <c r="C1" t="str">
-        <v>Título</v>
+        <v>Data agendada</v>
       </c>
       <c r="D1" t="str">
-        <v>Descrição</v>
+        <v>Situação</v>
       </c>
     </row>
     <row r="2">
@@ -855,13 +1090,13 @@
         <v>09/2026</v>
       </c>
       <c r="B2" t="str">
-        <v>Positivo</v>
+        <v>Indicação</v>
       </c>
       <c r="C2" t="str">
-        <v>Mais comparecimentos</v>
+        <v>02/10/2026</v>
       </c>
       <c r="D2" t="str">
-        <v>Os comparecimentos subiram em relação a agosto.</v>
+        <v>Aguardando atendimento</v>
       </c>
     </row>
     <row r="3">
@@ -869,13 +1104,13 @@
         <v>09/2026</v>
       </c>
       <c r="B3" t="str">
-        <v>Recomendação</v>
+        <v>Google</v>
       </c>
       <c r="C3" t="str">
-        <v>Reforçar indicação</v>
+        <v>28/10/2026</v>
       </c>
       <c r="D3" t="str">
-        <v>Indicação segue como o canal de maior conversão.</v>
+        <v>Aguardando atendimento</v>
       </c>
     </row>
   </sheetData>
@@ -883,4 +1118,73 @@
     <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="4.83203125" customWidth="1"/>
+    <col min="3" max="3" width="44.83203125" customWidth="1"/>
+    <col min="4" max="4" width="36.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Período</v>
+      </c>
+      <c r="B1" t="str">
+        <v>#</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Ação</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Impacto esperado</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Urgência</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>09/2026</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Script de triagem antes do contato comercial</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Menos contatos fora do perfil</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Alta</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>09/2026</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Reforçar a campanha que mais converteu</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Mais comparecimentos com a mesma verba</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Média</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/modelos/modelo-comercial.xlsx
+++ b/public/modelos/modelo-comercial.xlsx
@@ -14,7 +14,8 @@
     <sheet name="Plano de ação" sheetId="9" r:id="rId9"/>
     <sheet name="Indicadores" sheetId="10" r:id="rId10"/>
     <sheet name="Insights" sheetId="11" r:id="rId11"/>
-    <sheet name="Contexto" sheetId="12" r:id="rId12"/>
+    <sheet name="Comparativo" sheetId="12" r:id="rId12"/>
+    <sheet name="Contexto" sheetId="13" r:id="rId13"/>
   </sheets>
 </workbook>
 </file>
@@ -408,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A12"/>
   <cols>
     <col min="1" max="1" width="130.83203125" customWidth="1"/>
   </cols>
@@ -445,12 +446,12 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Detalhamentos: qualquer aba com números vira um ranking com o nome dela — Serviços, Profissionais, Terapeutas, Massagens, Procedimentos, Unidades… Colunas: o nome do item, Atendimentos (ou Quantidade), Receita e, se quiser, Status (Ativa, Inativa, Destaque).</v>
+        <v>Detalhamentos: qualquer aba com números vira uma aba do painel com o nome dela (ranking acumulado no ano) — Serviços, Profissionais, Terapeutas, Massagens, Procedimentos, Unidades… Colunas: o nome do item, Atendimentos (ou Quantidade), Receita e, se quiser, Status (Ativa, Inativa, Destaque).</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Tabelas livres: Oportunidades, Plano de ação, Próximos passos, Motivos de perda (ou qualquer aba sem números) aparecem como vieram, no mês.</v>
+        <v>Plano de ação (Prioridade, Ação, Detalhes) vira cartões na aba Insights. Outras tabelas sem números (Oportunidades, Motivos de perda…) aparecem como vieram, no mês.</v>
       </c>
     </row>
     <row r="9">
@@ -460,12 +461,22 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Insights — Tipo: Positivo, Atenção, Recomendação ou Neutro. Contexto: um aviso no topo do mês (ex.: mês parcial).</v>
+        <v>Insights — Tipo: Positivo, Atenção, Recomendação ou Neutro (define a cor). Tema (opcional): o selo do cartão, ex.: Recorrência, Terapeutas, ROI.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Comparativo — Indicador e Leitura: o comentário da Look ao lado de cada indicador no comparativo com o mês anterior (Leads, Receita, Ticket médio, ROI canais pagos…).</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Contexto: um aviso no mês em foco (ex.: Janeiro parcial), que também marca o mês na tabela mês a mês.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A12"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -524,12 +535,13 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,9 +552,12 @@
         <v>Tipo</v>
       </c>
       <c r="C1" t="str">
+        <v>Tema</v>
+      </c>
+      <c r="D1" t="str">
         <v>Título</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Descrição</v>
       </c>
     </row>
@@ -554,9 +569,12 @@
         <v>Positivo</v>
       </c>
       <c r="C2" t="str">
+        <v>Funil</v>
+      </c>
+      <c r="D2" t="str">
         <v>Mais comparecimentos</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>Os comparecimentos subiram em relação a agosto.</v>
       </c>
     </row>
@@ -568,20 +586,72 @@
         <v>Recomendação</v>
       </c>
       <c r="C3" t="str">
+        <v>Canais</v>
+      </c>
+      <c r="D3" t="str">
         <v>Reforçar indicação</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>Indicação segue como o canal de maior conversão.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="70.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Período</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Indicador</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Leitura</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>09/2026</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Leads</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Mais contatos com a mesma verba: a campanha nova entrou no dia 05.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>09/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Ticket médio</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Mais retornos no mix puxaram o ticket para baixo.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>
@@ -1122,13 +1192,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D3"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="4.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="44.83203125" customWidth="1"/>
-    <col min="4" max="4" width="36.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1136,55 +1205,46 @@
         <v>Período</v>
       </c>
       <c r="B1" t="str">
-        <v>#</v>
+        <v>Prioridade</v>
       </c>
       <c r="C1" t="str">
         <v>Ação</v>
       </c>
       <c r="D1" t="str">
-        <v>Impacto esperado</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Urgência</v>
+        <v>Detalhes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>09/2026</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="B2" t="str">
+        <v>1 · Triagem</v>
       </c>
       <c r="C2" t="str">
         <v>Script de triagem antes do contato comercial</v>
       </c>
       <c r="D2" t="str">
-        <v>Menos contatos fora do perfil</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Alta</v>
+        <v>Menos contatos fora do perfil e agenda mais qualificada.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>09/2026</v>
       </c>
-      <c r="B3">
-        <v>2</v>
+      <c r="B3" t="str">
+        <v>2 · Mídia</v>
       </c>
       <c r="C3" t="str">
         <v>Reforçar a campanha que mais converteu</v>
       </c>
       <c r="D3" t="str">
-        <v>Mais comparecimentos com a mesma verba</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Média</v>
+        <v>Mais comparecimentos com a mesma verba.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/modelos/modelo-comercial.xlsx
+++ b/public/modelos/modelo-comercial.xlsx
@@ -15,7 +15,8 @@
     <sheet name="Indicadores" sheetId="10" r:id="rId10"/>
     <sheet name="Insights" sheetId="11" r:id="rId11"/>
     <sheet name="Comparativo" sheetId="12" r:id="rId12"/>
-    <sheet name="Contexto" sheetId="13" r:id="rId13"/>
+    <sheet name="Notas" sheetId="13" r:id="rId13"/>
+    <sheet name="Contexto" sheetId="14" r:id="rId14"/>
   </sheets>
 </workbook>
 </file>
@@ -409,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A14"/>
   <cols>
     <col min="1" max="1" width="130.83203125" customWidth="1"/>
   </cols>
@@ -474,9 +475,19 @@
         <v>Contexto: um aviso no mês em foco (ex.: Janeiro parcial), que também marca o mês na tabela mês a mês.</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Notas — Seção e Texto: o destaque da Look ao lado de uma parte do painel (Funil, Receita por canal, Leads por canal, ROI, Canal a canal, Acumulado…). Nota sem lugar no painel aparece no fim de Insights.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Oportunidades (Origem, Data agendada, Situação): agenda já marcada para o mês seguinte — o portal calcula a receita potencial (quantidade × ticket do mês).</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -652,6 +663,55 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C3"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="90.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Período</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Seção</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Texto</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>09/2026</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Funil</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Com menos leads, os comparecimentos subiram: a qualificação no primeiro contato fez diferença.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>09/2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Receita por canal</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Indicação segue como a maior fonte de receita, sem custo de mídia.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
   <cols>
